--- a/demo/样例_对账函_甲辰建材.xlsx
+++ b/demo/样例_对账函_甲辰建材.xlsx
@@ -8,7 +8,7 @@
     <sheet sheetId="2" name="明细附页" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'对账函'!$A1:$F23</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'对账函'!$A1:$F24</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'明细附页'!$A1:$G8</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="37">
-  <si>
-    <t>邯郸市恒信机电设备有限公司</t>
-  </si>
-  <si>
-    <t>河北省邯郸市丛台区人民路 128 号 5 层　电话：0310-88886666</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="38">
+  <si>
+    <t>某市中和机电设备有限公司</t>
+  </si>
+  <si>
+    <t>某省省某市丛台区人民路 128 号 5 层　电话：0310-88886666</t>
   </si>
   <si>
     <t>应收账款对账函</t>
@@ -33,7 +33,7 @@
     <t>日期：2026年09月12日</t>
   </si>
   <si>
-    <t>致：邯郸市甲辰建材有限公司</t>
+    <t>致：某市甲辰建材有限公司</t>
   </si>
   <si>
     <t>为核实双方往来账目，现将我方账簿记录的本单位往来款项余额函告如下，请贵公司核对无误后在回函联签章寄回；如有不符，请在回函联中列明差异事项及金额。</t>
@@ -72,16 +72,19 @@
     <t>对方单位（签章）：__________________　　经办人：__________　　日期：____________</t>
   </si>
   <si>
-    <t>我方单位（盖章）：邯郸市恒信机电设备有限公司　　经办人：李会计　　日期：2026年09月12日</t>
+    <t>我方单位（盖章）：某市中和机电设备有限公司　　经办人：李会计　　日期：2026年09月12日</t>
   </si>
   <si>
     <t>本函仅用于双方核对往来款项余额，不构成任何债权债务的确认、变更或放弃。</t>
   </si>
   <si>
+    <t>数据来源：导入批次 imp_mtynaxb1004（原文件：s01_标准明细账_某市甲辰建材有限公司.xlsx）　余额口径：cumulative　明细笔数：4　生成时间：2026-09-13T01:14:48+08:00　版本：v1</t>
+  </si>
+  <si>
     <t>往来款项明细附页</t>
   </si>
   <si>
-    <t>单位：邯郸市甲辰建材有限公司　｜　截止日：2026-08-31　｜　编号：DZH-20260912-0001　｜　期初余额：0.00</t>
+    <t>单位：某市甲辰建材有限公司　｜　截止日：2026-08-31　｜　编号：DZH-20260912-0001　｜　期初余额：0.00</t>
   </si>
   <si>
     <t>序号</t>
@@ -133,7 +136,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -181,6 +184,11 @@
     <font>
       <color rgb="FF666666"/>
       <sz val="9"/>
+      <name val="宋体"/>
+    </font>
+    <font>
+      <color rgb="FF888888"/>
+      <sz val="8"/>
       <name val="宋体"/>
     </font>
     <font>
@@ -233,7 +241,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -272,7 +280,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -282,8 +293,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -626,7 +637,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -834,8 +845,18 @@
       <c r="E23" s="17"/>
       <c r="F23" s="17"/>
     </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+    </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="25">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:F4"/>
@@ -860,6 +881,7 @@
     <mergeCell ref="A20:F20"/>
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A24:F24"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.98" right="0.98" top="0.98" bottom="0.98" header="0.3" footer="0.3"/>
@@ -884,155 +906,155 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="A1" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
+      <c r="A2" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="20">
+      <c r="A4" s="21">
         <v>1</v>
       </c>
-      <c r="B4" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="21" t="s">
+      <c r="B4" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="22">
+      <c r="C4" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="23">
         <v>150000</v>
       </c>
-      <c r="E4" s="22" t="s">
+      <c r="E4" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="23">
         <v>150000</v>
       </c>
-      <c r="G4" s="20" t="s">
+      <c r="G4" s="21" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="20">
+      <c r="A5" s="21">
         <v>2</v>
       </c>
-      <c r="B5" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="21" t="s">
+      <c r="B5" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="C5" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="22">
+      <c r="E5" s="23">
         <v>100000</v>
       </c>
-      <c r="F5" s="22">
+      <c r="F5" s="23">
         <v>50000</v>
       </c>
-      <c r="G5" s="20" t="s">
+      <c r="G5" s="21" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="20">
+      <c r="A6" s="21">
         <v>3</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="23">
+        <v>80000</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="23">
+        <v>130000</v>
+      </c>
+      <c r="G6" s="21" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="21">
+        <v>4</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" s="22">
-        <v>80000</v>
-      </c>
-      <c r="E6" s="22" t="s">
+      <c r="D7" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="22">
-        <v>130000</v>
-      </c>
-      <c r="G6" s="20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="20">
-        <v>4</v>
-      </c>
-      <c r="B7" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="22">
+      <c r="E7" s="23">
         <v>60000</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="23">
         <v>70000</v>
       </c>
-      <c r="G7" s="20" t="s">
+      <c r="G7" s="21" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
-      <c r="D8" s="23">
+      <c r="D8" s="24">
         <v>230000</v>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="24">
         <v>160000</v>
       </c>
-      <c r="F8" s="23">
+      <c r="F8" s="24">
         <v>70000</v>
       </c>
       <c r="G8" s="16" t="s">
